--- a/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 14,84</t>
+          <t>5,6; 14,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,81</t>
+          <t>4,87; 12,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 12,12</t>
+          <t>5,92; 11,7</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,93</t>
+          <t>4,77; 10,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 15,93</t>
+          <t>8,63; 16,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,8</t>
+          <t>7,66; 12,62</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,29</t>
+          <t>2,63; 9,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 8,66</t>
+          <t>2,74; 8,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,0</t>
+          <t>3,37; 8,06</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 19,81</t>
+          <t>9,77; 19,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,28</t>
+          <t>5,6; 13,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,65</t>
+          <t>8,7; 14,64</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,0</t>
+          <t>6,98; 10,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 10,96</t>
+          <t>7,24; 10,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,42</t>
+          <t>7,63; 10,34</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>11137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22033</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6512; 16297</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6638; 17486</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14964; 29555</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13727</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43963</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8906; 20129</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21690; 41170</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>33571; 55290</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10244</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9656</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4941; 16976</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4910; 16040</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12387; 29595</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>23012</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15485</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38497</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>15727; 31018</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>9932; 23614</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>29430; 49529</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>58120</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66273</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124393</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>45492; 71648</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>53846; 81387</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>106580; 144431</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 14,01</t>
+          <t>5,94; 14,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 12,83</t>
+          <t>4,6; 12,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 11,7</t>
+          <t>6,13; 12,28</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,77</t>
+          <t>4,56; 10,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 16,39</t>
+          <t>8,4; 16,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,62</t>
+          <t>7,73; 13,06</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,03</t>
+          <t>2,76; 9,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,95</t>
+          <t>3,1; 9,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,06</t>
+          <t>3,46; 8,09</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 19,27</t>
+          <t>10,15; 20,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,6; 13,32</t>
+          <t>5,68; 13,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 14,64</t>
+          <t>8,73; 15,05</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,99</t>
+          <t>6,75; 11,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,94</t>
+          <t>7,25; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,34</t>
+          <t>7,56; 10,33</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6512; 16297</t>
+          <t>6909; 16948</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6638; 17486</t>
+          <t>6273; 16662</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14964; 29555</t>
+          <t>15486; 31023</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8906; 20129</t>
+          <t>8518; 20499</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21690; 41170</t>
+          <t>21106; 40983</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33571; 55290</t>
+          <t>33847; 57222</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4941; 16976</t>
+          <t>5189; 17057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4910; 16040</t>
+          <t>5554; 16643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12387; 29595</t>
+          <t>12697; 29711</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15727; 31018</t>
+          <t>16339; 32330</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9932; 23614</t>
+          <t>10072; 23475</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29430; 49529</t>
+          <t>29543; 50889</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45492; 71648</t>
+          <t>43995; 71708</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53846; 81387</t>
+          <t>53950; 82476</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106580; 144431</t>
+          <t>105592; 144159</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 14,57</t>
+          <t>4,98; 14,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,22</t>
+          <t>5,84; 14,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 12,28</t>
+          <t>6,39; 12,66</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,97</t>
+          <t>9,04; 16,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 16,31</t>
+          <t>4,86; 11,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,06</t>
+          <t>7,84; 13,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,07</t>
+          <t>2,96; 9,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,28</t>
+          <t>4,08; 11,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,09</t>
+          <t>4,17; 9,37</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 20,08</t>
+          <t>5,58; 13,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,24</t>
+          <t>10,51; 20,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 15,05</t>
+          <t>9,43; 15,55</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,0</t>
+          <t>7,62; 11,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,08</t>
+          <t>7,88; 12,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,33</t>
+          <t>8,1; 10,99</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>21972</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6909; 16948</t>
+          <t>6060; 17238</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6273; 16662</t>
+          <t>7026; 18018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15486; 31023</t>
+          <t>15473; 30653</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>29754</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>43084</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8518; 20499</t>
+          <t>21101; 39574</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21106; 40983</t>
+          <t>8791; 20220</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33847; 57222</t>
+          <t>32485; 54216</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>19756</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5189; 17057</t>
+          <t>4794; 14958</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5554; 16643</t>
+          <t>6306; 18384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12697; 29711</t>
+          <t>13214; 29663</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>15038</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>23825</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>38863</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16339; 32330</t>
+          <t>9266; 23053</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10072; 23475</t>
+          <t>16928; 32535</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29543; 50889</t>
+          <t>30827; 50824</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>64371</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>66273</t>
+          <t>59305</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124393</t>
+          <t>123676</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43995; 71708</t>
+          <t>52080; 79556</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53950; 82476</t>
+          <t>48592; 74042</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>105592; 144159</t>
+          <t>105345; 142901</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$recibos_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,98; 14,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,84; 14,98</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,39; 12,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>9,04; 16,95</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,86; 11,18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7,84; 13,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,96; 9,24</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,08; 11,88</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,17; 9,37</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14,8%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,58; 13,89</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10,51; 20,21</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 15,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9,61%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,62; 11,65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,88; 12,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8,1; 10,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.08637471984143619</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.09517338240553737</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.09074696770707491</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10521</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>11451</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21972</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.04975096587445818</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.05839719784576666</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.06390663906025762</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6060; 17238</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7026; 18018</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15473; 30653</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1415158621525537</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1497516321485292</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1265987720610048</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1274199353353069</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.0737019461672925</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1039729332269092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>29754</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13330</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43084</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.09036683600194936</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.04860502776421691</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.07839499472773251</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>21101; 39574</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8791; 20220</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32485; 54216</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1694755352062029</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1117937714056067</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1308378510466881</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.05597031893144202</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.06914121543011591</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.06240778274303473</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9058</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>10698</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19756</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.02962155835211116</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.04075378031570012</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.04174206515798528</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4794; 14958</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6306; 18384</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13214; 29663</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.09242118287741605</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.118813524321637</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.09370283080528663</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.09063010740516569</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1479897961492303</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1188768025033867</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>15038</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23825</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38863</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.05584388308394214</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1051495182739071</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.09429542314784344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>9266; 23053</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>16928; 32535</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30827; 50824</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1389337796129902</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2020920184740858</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1554646088725523</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.09423580116271311</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.0961323140674791</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.09513578263351097</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>64371</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>59305</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>123676</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.07624276757825967</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07876727035487753</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.08103488366238508</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>52080; 79556</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>48592; 74042</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>105345; 142901</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1164652119498361</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1200224591607166</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.109924892575159</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago de recibos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10521</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11451</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>21972</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6060</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>7026</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>15473</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>17238</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18018</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>30653</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>29754</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>13330</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>43084</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>21101</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>8791</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>32485</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>39574</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>20220</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>54216</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>9058</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>10698</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>19756</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>4794</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>6306</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>13214</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>14958</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>18384</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>29663</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>15038</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>23825</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>38863</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>9266</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>16928</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>30827</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>23053</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>32535</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>50824</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>64371</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>59305</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>123676</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>52080</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>48592</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>105345</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>79556</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>74042</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>142901</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>